--- a/作业反馈/HTML作业提交情况.xlsx
+++ b/作业反馈/HTML作业提交情况.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\surface\Documents\Sync\Teaching\本学期\选课名单\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\surface\Documents\GitHub\HTML\作业反馈\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -454,9 +454,6 @@
   </si>
   <si>
     <t>B16041511</t>
-  </si>
-  <si>
-    <t>仲柯尔</t>
   </si>
   <si>
     <t>47</t>
@@ -795,12 +792,24 @@
   <si>
     <t>邓治国</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仲柯尔（仲宣）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -820,12 +829,6 @@
     <font>
       <sz val="16"/>
       <name val="黑体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -1146,20 +1149,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CV77"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="5.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.4375" customWidth="1"/>
+    <col min="4" max="4" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" ht="20.399999999999999" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:100" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1261,7 +1264,7 @@
       <c r="CU1" s="1"/>
       <c r="CV1" s="1"/>
     </row>
-    <row r="2" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1278,22 +1281,22 @@
         <v>4</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1385,13 +1388,13 @@
       <c r="CU2" s="1"/>
       <c r="CV2" s="1"/>
     </row>
-    <row r="3" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1399,9 +1402,11 @@
         <v>1</v>
       </c>
       <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1495,7 +1500,7 @@
       <c r="CU3" s="1"/>
       <c r="CV3" s="1"/>
     </row>
-    <row r="4" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1517,7 +1522,9 @@
       <c r="G4" s="2">
         <v>0</v>
       </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1611,7 +1618,7 @@
       <c r="CU4" s="1"/>
       <c r="CV4" s="1"/>
     </row>
-    <row r="5" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1633,7 +1640,9 @@
       <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1727,7 +1736,7 @@
       <c r="CU5" s="1"/>
       <c r="CV5" s="1"/>
     </row>
-    <row r="6" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -1749,7 +1758,9 @@
       <c r="G6" s="2">
         <v>1</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1843,7 +1854,7 @@
       <c r="CU6" s="1"/>
       <c r="CV6" s="1"/>
     </row>
-    <row r="7" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1865,7 +1876,9 @@
       <c r="G7" s="2">
         <v>1</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1959,7 +1972,7 @@
       <c r="CU7" s="1"/>
       <c r="CV7" s="1"/>
     </row>
-    <row r="8" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1981,7 +1994,9 @@
       <c r="G8" s="2">
         <v>1</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -2075,7 +2090,7 @@
       <c r="CU8" s="1"/>
       <c r="CV8" s="1"/>
     </row>
-    <row r="9" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -2097,7 +2112,9 @@
       <c r="G9" s="2">
         <v>1</v>
       </c>
-      <c r="H9" s="2"/>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2191,7 +2208,7 @@
       <c r="CU9" s="1"/>
       <c r="CV9" s="1"/>
     </row>
-    <row r="10" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -2213,7 +2230,9 @@
       <c r="G10" s="2">
         <v>1</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -2307,7 +2326,7 @@
       <c r="CU10" s="1"/>
       <c r="CV10" s="1"/>
     </row>
-    <row r="11" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -2329,7 +2348,9 @@
       <c r="G11" s="2">
         <v>1</v>
       </c>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2423,7 +2444,7 @@
       <c r="CU11" s="1"/>
       <c r="CV11" s="1"/>
     </row>
-    <row r="12" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -2445,7 +2466,9 @@
       <c r="G12" s="2">
         <v>1</v>
       </c>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2539,7 +2562,7 @@
       <c r="CU12" s="1"/>
       <c r="CV12" s="1"/>
     </row>
-    <row r="13" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
         <v>35</v>
       </c>
@@ -2561,7 +2584,9 @@
       <c r="G13" s="2">
         <v>1</v>
       </c>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2655,7 +2680,7 @@
       <c r="CU13" s="1"/>
       <c r="CV13" s="1"/>
     </row>
-    <row r="14" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
         <v>38</v>
       </c>
@@ -2677,7 +2702,9 @@
       <c r="G14" s="2">
         <v>1</v>
       </c>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2771,7 +2798,7 @@
       <c r="CU14" s="1"/>
       <c r="CV14" s="1"/>
     </row>
-    <row r="15" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -2793,7 +2820,9 @@
       <c r="G15" s="2">
         <v>0</v>
       </c>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -2887,7 +2916,7 @@
       <c r="CU15" s="1"/>
       <c r="CV15" s="1"/>
     </row>
-    <row r="16" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
         <v>44</v>
       </c>
@@ -2909,7 +2938,9 @@
       <c r="G16" s="2">
         <v>1</v>
       </c>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2">
+        <v>1</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -3003,7 +3034,7 @@
       <c r="CU16" s="1"/>
       <c r="CV16" s="1"/>
     </row>
-    <row r="17" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
@@ -3025,7 +3056,9 @@
       <c r="G17" s="2">
         <v>1</v>
       </c>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -3119,7 +3152,7 @@
       <c r="CU17" s="1"/>
       <c r="CV17" s="1"/>
     </row>
-    <row r="18" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>50</v>
       </c>
@@ -3141,7 +3174,9 @@
       <c r="G18" s="2">
         <v>1</v>
       </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3235,7 +3270,7 @@
       <c r="CU18" s="1"/>
       <c r="CV18" s="1"/>
     </row>
-    <row r="19" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
         <v>53</v>
       </c>
@@ -3257,7 +3292,9 @@
       <c r="G19" s="2">
         <v>1</v>
       </c>
-      <c r="H19" s="2"/>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3351,7 +3388,7 @@
       <c r="CU19" s="1"/>
       <c r="CV19" s="1"/>
     </row>
-    <row r="20" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>56</v>
       </c>
@@ -3373,7 +3410,9 @@
       <c r="G20" s="2">
         <v>1</v>
       </c>
-      <c r="H20" s="2"/>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -3467,7 +3506,7 @@
       <c r="CU20" s="1"/>
       <c r="CV20" s="1"/>
     </row>
-    <row r="21" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>59</v>
       </c>
@@ -3489,7 +3528,9 @@
       <c r="G21" s="2">
         <v>1</v>
       </c>
-      <c r="H21" s="2"/>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -3583,7 +3624,7 @@
       <c r="CU21" s="1"/>
       <c r="CV21" s="1"/>
     </row>
-    <row r="22" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
         <v>62</v>
       </c>
@@ -3605,7 +3646,9 @@
       <c r="G22" s="2">
         <v>1</v>
       </c>
-      <c r="H22" s="2"/>
+      <c r="H22" s="2">
+        <v>1</v>
+      </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -3699,7 +3742,7 @@
       <c r="CU22" s="1"/>
       <c r="CV22" s="1"/>
     </row>
-    <row r="23" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
         <v>65</v>
       </c>
@@ -3721,7 +3764,9 @@
       <c r="G23" s="2">
         <v>1</v>
       </c>
-      <c r="H23" s="2"/>
+      <c r="H23" s="2">
+        <v>1</v>
+      </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -3815,7 +3860,7 @@
       <c r="CU23" s="1"/>
       <c r="CV23" s="1"/>
     </row>
-    <row r="24" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
         <v>68</v>
       </c>
@@ -3837,7 +3882,9 @@
       <c r="G24" s="2">
         <v>1</v>
       </c>
-      <c r="H24" s="2"/>
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -3931,7 +3978,7 @@
       <c r="CU24" s="1"/>
       <c r="CV24" s="1"/>
     </row>
-    <row r="25" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
         <v>71</v>
       </c>
@@ -3953,7 +4000,9 @@
       <c r="G25" s="2">
         <v>1</v>
       </c>
-      <c r="H25" s="2"/>
+      <c r="H25" s="2">
+        <v>1</v>
+      </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -4047,7 +4096,7 @@
       <c r="CU25" s="1"/>
       <c r="CV25" s="1"/>
     </row>
-    <row r="26" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
         <v>74</v>
       </c>
@@ -4069,7 +4118,9 @@
       <c r="G26" s="2">
         <v>1</v>
       </c>
-      <c r="H26" s="2"/>
+      <c r="H26" s="2">
+        <v>1</v>
+      </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -4163,7 +4214,7 @@
       <c r="CU26" s="1"/>
       <c r="CV26" s="1"/>
     </row>
-    <row r="27" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
         <v>77</v>
       </c>
@@ -4185,7 +4236,9 @@
       <c r="G27" s="2">
         <v>0</v>
       </c>
-      <c r="H27" s="2"/>
+      <c r="H27" s="2">
+        <v>0</v>
+      </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4279,7 +4332,7 @@
       <c r="CU27" s="1"/>
       <c r="CV27" s="1"/>
     </row>
-    <row r="28" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
         <v>80</v>
       </c>
@@ -4301,7 +4354,9 @@
       <c r="G28" s="2">
         <v>0</v>
       </c>
-      <c r="H28" s="2"/>
+      <c r="H28" s="2">
+        <v>0</v>
+      </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -4395,7 +4450,7 @@
       <c r="CU28" s="1"/>
       <c r="CV28" s="1"/>
     </row>
-    <row r="29" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
         <v>83</v>
       </c>
@@ -4417,7 +4472,9 @@
       <c r="G29" s="2">
         <v>1</v>
       </c>
-      <c r="H29" s="2"/>
+      <c r="H29" s="2">
+        <v>1</v>
+      </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -4511,7 +4568,7 @@
       <c r="CU29" s="1"/>
       <c r="CV29" s="1"/>
     </row>
-    <row r="30" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
         <v>86</v>
       </c>
@@ -4533,7 +4590,9 @@
       <c r="G30" s="2">
         <v>1</v>
       </c>
-      <c r="H30" s="2"/>
+      <c r="H30" s="2">
+        <v>1</v>
+      </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -4627,7 +4686,7 @@
       <c r="CU30" s="1"/>
       <c r="CV30" s="1"/>
     </row>
-    <row r="31" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
         <v>89</v>
       </c>
@@ -4649,7 +4708,9 @@
       <c r="G31" s="2">
         <v>1</v>
       </c>
-      <c r="H31" s="2"/>
+      <c r="H31" s="2">
+        <v>1</v>
+      </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -4743,7 +4804,7 @@
       <c r="CU31" s="1"/>
       <c r="CV31" s="1"/>
     </row>
-    <row r="32" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>92</v>
       </c>
@@ -4765,7 +4826,9 @@
       <c r="G32" s="2">
         <v>1</v>
       </c>
-      <c r="H32" s="2"/>
+      <c r="H32" s="2">
+        <v>1</v>
+      </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
@@ -4859,7 +4922,7 @@
       <c r="CU32" s="1"/>
       <c r="CV32" s="1"/>
     </row>
-    <row r="33" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>95</v>
       </c>
@@ -4881,7 +4944,9 @@
       <c r="G33" s="2">
         <v>1</v>
       </c>
-      <c r="H33" s="2"/>
+      <c r="H33" s="2">
+        <v>1</v>
+      </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -4975,7 +5040,7 @@
       <c r="CU33" s="1"/>
       <c r="CV33" s="1"/>
     </row>
-    <row r="34" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
         <v>98</v>
       </c>
@@ -4997,7 +5062,9 @@
       <c r="G34" s="2">
         <v>1</v>
       </c>
-      <c r="H34" s="2"/>
+      <c r="H34" s="2">
+        <v>1</v>
+      </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -5091,7 +5158,7 @@
       <c r="CU34" s="1"/>
       <c r="CV34" s="1"/>
     </row>
-    <row r="35" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>101</v>
       </c>
@@ -5113,7 +5180,9 @@
       <c r="G35" s="2">
         <v>1</v>
       </c>
-      <c r="H35" s="2"/>
+      <c r="H35" s="2">
+        <v>1</v>
+      </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
@@ -5207,7 +5276,7 @@
       <c r="CU35" s="1"/>
       <c r="CV35" s="1"/>
     </row>
-    <row r="36" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>104</v>
       </c>
@@ -5229,7 +5298,9 @@
       <c r="G36" s="2">
         <v>1</v>
       </c>
-      <c r="H36" s="2"/>
+      <c r="H36" s="2">
+        <v>1</v>
+      </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -5323,7 +5394,7 @@
       <c r="CU36" s="1"/>
       <c r="CV36" s="1"/>
     </row>
-    <row r="37" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
         <v>107</v>
       </c>
@@ -5345,7 +5416,9 @@
       <c r="G37" s="2">
         <v>1</v>
       </c>
-      <c r="H37" s="2"/>
+      <c r="H37" s="2">
+        <v>1</v>
+      </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -5439,7 +5512,7 @@
       <c r="CU37" s="1"/>
       <c r="CV37" s="1"/>
     </row>
-    <row r="38" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>110</v>
       </c>
@@ -5461,7 +5534,9 @@
       <c r="G38" s="2">
         <v>1</v>
       </c>
-      <c r="H38" s="2"/>
+      <c r="H38" s="2">
+        <v>1</v>
+      </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
@@ -5555,7 +5630,7 @@
       <c r="CU38" s="1"/>
       <c r="CV38" s="1"/>
     </row>
-    <row r="39" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>113</v>
       </c>
@@ -5577,7 +5652,9 @@
       <c r="G39" s="2">
         <v>0</v>
       </c>
-      <c r="H39" s="2"/>
+      <c r="H39" s="2">
+        <v>0</v>
+      </c>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -5671,7 +5748,7 @@
       <c r="CU39" s="1"/>
       <c r="CV39" s="1"/>
     </row>
-    <row r="40" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>116</v>
       </c>
@@ -5693,7 +5770,9 @@
       <c r="G40" s="2">
         <v>1</v>
       </c>
-      <c r="H40" s="2"/>
+      <c r="H40" s="2">
+        <v>1</v>
+      </c>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
@@ -5787,7 +5866,7 @@
       <c r="CU40" s="1"/>
       <c r="CV40" s="1"/>
     </row>
-    <row r="41" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>119</v>
       </c>
@@ -5809,7 +5888,9 @@
       <c r="G41" s="2">
         <v>1</v>
       </c>
-      <c r="H41" s="2"/>
+      <c r="H41" s="2">
+        <v>1</v>
+      </c>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
@@ -5903,7 +5984,7 @@
       <c r="CU41" s="1"/>
       <c r="CV41" s="1"/>
     </row>
-    <row r="42" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>122</v>
       </c>
@@ -5925,7 +6006,9 @@
       <c r="G42" s="2">
         <v>1</v>
       </c>
-      <c r="H42" s="2"/>
+      <c r="H42" s="2">
+        <v>1</v>
+      </c>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -6019,7 +6102,7 @@
       <c r="CU42" s="1"/>
       <c r="CV42" s="1"/>
     </row>
-    <row r="43" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A43" s="2" t="s">
         <v>125</v>
       </c>
@@ -6041,7 +6124,9 @@
       <c r="G43" s="2">
         <v>1</v>
       </c>
-      <c r="H43" s="2"/>
+      <c r="H43" s="2">
+        <v>1</v>
+      </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -6135,7 +6220,7 @@
       <c r="CU43" s="1"/>
       <c r="CV43" s="1"/>
     </row>
-    <row r="44" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A44" s="2" t="s">
         <v>128</v>
       </c>
@@ -6157,7 +6242,9 @@
       <c r="G44" s="2">
         <v>1</v>
       </c>
-      <c r="H44" s="2"/>
+      <c r="H44" s="2">
+        <v>1</v>
+      </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
@@ -6251,7 +6338,7 @@
       <c r="CU44" s="1"/>
       <c r="CV44" s="1"/>
     </row>
-    <row r="45" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A45" s="2" t="s">
         <v>131</v>
       </c>
@@ -6273,7 +6360,9 @@
       <c r="G45" s="2">
         <v>1</v>
       </c>
-      <c r="H45" s="2"/>
+      <c r="H45" s="2">
+        <v>1</v>
+      </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
@@ -6367,7 +6456,7 @@
       <c r="CU45" s="1"/>
       <c r="CV45" s="1"/>
     </row>
-    <row r="46" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A46" s="2" t="s">
         <v>134</v>
       </c>
@@ -6389,7 +6478,9 @@
       <c r="G46" s="2">
         <v>1</v>
       </c>
-      <c r="H46" s="2"/>
+      <c r="H46" s="2">
+        <v>1</v>
+      </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -6483,7 +6574,7 @@
       <c r="CU46" s="1"/>
       <c r="CV46" s="1"/>
     </row>
-    <row r="47" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A47" s="2" t="s">
         <v>137</v>
       </c>
@@ -6505,7 +6596,9 @@
       <c r="G47" s="2">
         <v>0</v>
       </c>
-      <c r="H47" s="2"/>
+      <c r="H47" s="2">
+        <v>1</v>
+      </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
@@ -6599,7 +6692,7 @@
       <c r="CU47" s="1"/>
       <c r="CV47" s="1"/>
     </row>
-    <row r="48" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A48" s="2" t="s">
         <v>140</v>
       </c>
@@ -6621,7 +6714,9 @@
       <c r="G48" s="2">
         <v>1</v>
       </c>
-      <c r="H48" s="2"/>
+      <c r="H48" s="2">
+        <v>1</v>
+      </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
@@ -6715,7 +6810,7 @@
       <c r="CU48" s="1"/>
       <c r="CV48" s="1"/>
     </row>
-    <row r="49" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A49" s="2" t="s">
         <v>143</v>
       </c>
@@ -6723,7 +6818,7 @@
         <v>144</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>145</v>
+        <v>223</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>8</v>
@@ -6737,7 +6832,9 @@
       <c r="G49" s="2">
         <v>0</v>
       </c>
-      <c r="H49" s="2"/>
+      <c r="H49" s="2">
+        <v>1</v>
+      </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
@@ -6831,15 +6928,15 @@
       <c r="CU49" s="1"/>
       <c r="CV49" s="1"/>
     </row>
-    <row r="50" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>8</v>
@@ -6853,7 +6950,9 @@
       <c r="G50" s="2">
         <v>1</v>
       </c>
-      <c r="H50" s="2"/>
+      <c r="H50" s="2">
+        <v>1</v>
+      </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
@@ -6947,15 +7046,15 @@
       <c r="CU50" s="1"/>
       <c r="CV50" s="1"/>
     </row>
-    <row r="51" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A51" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>8</v>
@@ -6969,7 +7068,9 @@
       <c r="G51" s="2">
         <v>1</v>
       </c>
-      <c r="H51" s="2"/>
+      <c r="H51" s="2">
+        <v>1</v>
+      </c>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -7063,15 +7164,15 @@
       <c r="CU51" s="1"/>
       <c r="CV51" s="1"/>
     </row>
-    <row r="52" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A52" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>8</v>
@@ -7085,7 +7186,9 @@
       <c r="G52" s="2">
         <v>0</v>
       </c>
-      <c r="H52" s="2"/>
+      <c r="H52" s="2">
+        <v>0</v>
+      </c>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -7179,15 +7282,15 @@
       <c r="CU52" s="1"/>
       <c r="CV52" s="1"/>
     </row>
-    <row r="53" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A53" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>8</v>
@@ -7201,7 +7304,9 @@
       <c r="G53" s="2">
         <v>1</v>
       </c>
-      <c r="H53" s="2"/>
+      <c r="H53" s="2">
+        <v>1</v>
+      </c>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -7295,15 +7400,15 @@
       <c r="CU53" s="1"/>
       <c r="CV53" s="1"/>
     </row>
-    <row r="54" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A54" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>8</v>
@@ -7317,7 +7422,9 @@
       <c r="G54" s="2">
         <v>1</v>
       </c>
-      <c r="H54" s="2"/>
+      <c r="H54" s="2">
+        <v>1</v>
+      </c>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -7411,15 +7518,15 @@
       <c r="CU54" s="1"/>
       <c r="CV54" s="1"/>
     </row>
-    <row r="55" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A55" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>8</v>
@@ -7433,7 +7540,9 @@
       <c r="G55" s="2">
         <v>1</v>
       </c>
-      <c r="H55" s="2"/>
+      <c r="H55" s="2">
+        <v>1</v>
+      </c>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -7527,15 +7636,15 @@
       <c r="CU55" s="1"/>
       <c r="CV55" s="1"/>
     </row>
-    <row r="56" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A56" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>8</v>
@@ -7549,7 +7658,9 @@
       <c r="G56" s="2">
         <v>1</v>
       </c>
-      <c r="H56" s="2"/>
+      <c r="H56" s="2">
+        <v>1</v>
+      </c>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -7643,15 +7754,15 @@
       <c r="CU56" s="1"/>
       <c r="CV56" s="1"/>
     </row>
-    <row r="57" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A57" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>8</v>
@@ -7665,7 +7776,9 @@
       <c r="G57" s="2">
         <v>1</v>
       </c>
-      <c r="H57" s="2"/>
+      <c r="H57" s="2">
+        <v>1</v>
+      </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -7759,15 +7872,15 @@
       <c r="CU57" s="1"/>
       <c r="CV57" s="1"/>
     </row>
-    <row r="58" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A58" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>8</v>
@@ -7781,7 +7894,9 @@
       <c r="G58" s="2">
         <v>1</v>
       </c>
-      <c r="H58" s="2"/>
+      <c r="H58" s="2">
+        <v>1</v>
+      </c>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -7875,15 +7990,15 @@
       <c r="CU58" s="1"/>
       <c r="CV58" s="1"/>
     </row>
-    <row r="59" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A59" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>8</v>
@@ -7897,7 +8012,9 @@
       <c r="G59" s="2">
         <v>1</v>
       </c>
-      <c r="H59" s="2"/>
+      <c r="H59" s="2">
+        <v>1</v>
+      </c>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -7991,15 +8108,15 @@
       <c r="CU59" s="1"/>
       <c r="CV59" s="1"/>
     </row>
-    <row r="60" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A60" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>8</v>
@@ -8013,7 +8130,9 @@
       <c r="G60" s="2">
         <v>1</v>
       </c>
-      <c r="H60" s="2"/>
+      <c r="H60" s="2">
+        <v>1</v>
+      </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
@@ -8107,15 +8226,15 @@
       <c r="CU60" s="1"/>
       <c r="CV60" s="1"/>
     </row>
-    <row r="61" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A61" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>8</v>
@@ -8129,7 +8248,9 @@
       <c r="G61" s="2">
         <v>1</v>
       </c>
-      <c r="H61" s="2"/>
+      <c r="H61" s="2">
+        <v>1</v>
+      </c>
       <c r="I61" s="2"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
@@ -8223,15 +8344,15 @@
       <c r="CU61" s="1"/>
       <c r="CV61" s="1"/>
     </row>
-    <row r="62" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A62" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>8</v>
@@ -8245,7 +8366,9 @@
       <c r="G62" s="2">
         <v>1</v>
       </c>
-      <c r="H62" s="2"/>
+      <c r="H62" s="2">
+        <v>1</v>
+      </c>
       <c r="I62" s="2"/>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
@@ -8339,15 +8462,15 @@
       <c r="CU62" s="1"/>
       <c r="CV62" s="1"/>
     </row>
-    <row r="63" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A63" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>8</v>
@@ -8361,7 +8484,9 @@
       <c r="G63" s="2">
         <v>0</v>
       </c>
-      <c r="H63" s="2"/>
+      <c r="H63" s="2">
+        <v>1</v>
+      </c>
       <c r="I63" s="2"/>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
@@ -8455,15 +8580,15 @@
       <c r="CU63" s="1"/>
       <c r="CV63" s="1"/>
     </row>
-    <row r="64" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A64" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>8</v>
@@ -8477,7 +8602,9 @@
       <c r="G64" s="2">
         <v>1</v>
       </c>
-      <c r="H64" s="2"/>
+      <c r="H64" s="2">
+        <v>1</v>
+      </c>
       <c r="I64" s="2"/>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
@@ -8571,15 +8698,15 @@
       <c r="CU64" s="1"/>
       <c r="CV64" s="1"/>
     </row>
-    <row r="65" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A65" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>8</v>
@@ -8593,7 +8720,9 @@
       <c r="G65" s="2">
         <v>1</v>
       </c>
-      <c r="H65" s="2"/>
+      <c r="H65" s="2">
+        <v>1</v>
+      </c>
       <c r="I65" s="2"/>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
@@ -8687,15 +8816,15 @@
       <c r="CU65" s="1"/>
       <c r="CV65" s="1"/>
     </row>
-    <row r="66" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A66" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>8</v>
@@ -8709,7 +8838,9 @@
       <c r="G66" s="2">
         <v>1</v>
       </c>
-      <c r="H66" s="2"/>
+      <c r="H66" s="2">
+        <v>1</v>
+      </c>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
@@ -8803,15 +8934,15 @@
       <c r="CU66" s="1"/>
       <c r="CV66" s="1"/>
     </row>
-    <row r="67" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A67" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>8</v>
@@ -8825,7 +8956,9 @@
       <c r="G67" s="2">
         <v>1</v>
       </c>
-      <c r="H67" s="2"/>
+      <c r="H67" s="2">
+        <v>1</v>
+      </c>
       <c r="I67" s="2"/>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
@@ -8919,15 +9052,15 @@
       <c r="CU67" s="1"/>
       <c r="CV67" s="1"/>
     </row>
-    <row r="68" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A68" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>8</v>
@@ -8941,7 +9074,9 @@
       <c r="G68" s="2">
         <v>1</v>
       </c>
-      <c r="H68" s="2"/>
+      <c r="H68" s="2">
+        <v>1</v>
+      </c>
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
@@ -9035,15 +9170,15 @@
       <c r="CU68" s="1"/>
       <c r="CV68" s="1"/>
     </row>
-    <row r="69" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A69" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>8</v>
@@ -9057,7 +9192,9 @@
       <c r="G69" s="2">
         <v>1</v>
       </c>
-      <c r="H69" s="2"/>
+      <c r="H69" s="2">
+        <v>1</v>
+      </c>
       <c r="I69" s="2"/>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
@@ -9151,15 +9288,15 @@
       <c r="CU69" s="1"/>
       <c r="CV69" s="1"/>
     </row>
-    <row r="70" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A70" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>8</v>
@@ -9173,7 +9310,9 @@
       <c r="G70" s="2">
         <v>1</v>
       </c>
-      <c r="H70" s="2"/>
+      <c r="H70" s="2">
+        <v>1</v>
+      </c>
       <c r="I70" s="2"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
@@ -9267,15 +9406,15 @@
       <c r="CU70" s="1"/>
       <c r="CV70" s="1"/>
     </row>
-    <row r="71" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A71" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>8</v>
@@ -9289,7 +9428,9 @@
       <c r="G71" s="2">
         <v>1</v>
       </c>
-      <c r="H71" s="2"/>
+      <c r="H71" s="2">
+        <v>1</v>
+      </c>
       <c r="I71" s="2"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
@@ -9383,15 +9524,15 @@
       <c r="CU71" s="1"/>
       <c r="CV71" s="1"/>
     </row>
-    <row r="72" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A72" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>8</v>
@@ -9405,7 +9546,9 @@
       <c r="G72" s="2">
         <v>1</v>
       </c>
-      <c r="H72" s="2"/>
+      <c r="H72" s="2">
+        <v>1</v>
+      </c>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
@@ -9499,7 +9642,7 @@
       <c r="CU72" s="1"/>
       <c r="CV72" s="1"/>
     </row>
-    <row r="73" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -9601,7 +9744,7 @@
       <c r="CU73" s="1"/>
       <c r="CV73" s="1"/>
     </row>
-    <row r="74" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -9703,7 +9846,7 @@
       <c r="CU74" s="1"/>
       <c r="CV74" s="1"/>
     </row>
-    <row r="75" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -9805,7 +9948,7 @@
       <c r="CU75" s="1"/>
       <c r="CV75" s="1"/>
     </row>
-    <row r="76" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -9907,7 +10050,7 @@
       <c r="CU76" s="1"/>
       <c r="CV76" s="1"/>
     </row>
-    <row r="77" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:100" x14ac:dyDescent="0.4">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>

--- a/作业反馈/HTML作业提交情况.xlsx
+++ b/作业反馈/HTML作业提交情况.xlsx
@@ -1149,18 +1149,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:CV77"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.4375" customWidth="1"/>
-    <col min="4" max="4" width="26.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" customWidth="1"/>
+    <col min="4" max="4" width="26.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" ht="20.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:100" ht="20.399999999999999" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>214</v>
       </c>
@@ -1264,7 +1264,7 @@
       <c r="CU1" s="1"/>
       <c r="CV1" s="1"/>
     </row>
-    <row r="2" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1388,7 +1388,7 @@
       <c r="CU2" s="1"/>
       <c r="CV2" s="1"/>
     </row>
-    <row r="3" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>221</v>
@@ -1407,7 +1407,9 @@
       <c r="H3" s="2">
         <v>1</v>
       </c>
-      <c r="I3" s="2"/>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="1"/>
@@ -1500,7 +1502,7 @@
       <c r="CU3" s="1"/>
       <c r="CV3" s="1"/>
     </row>
-    <row r="4" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1525,7 +1527,9 @@
       <c r="H4" s="2">
         <v>0</v>
       </c>
-      <c r="I4" s="2"/>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="1"/>
@@ -1618,7 +1622,7 @@
       <c r="CU4" s="1"/>
       <c r="CV4" s="1"/>
     </row>
-    <row r="5" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1643,7 +1647,9 @@
       <c r="H5" s="2">
         <v>1</v>
       </c>
-      <c r="I5" s="2"/>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="1"/>
@@ -1736,7 +1742,7 @@
       <c r="CU5" s="1"/>
       <c r="CV5" s="1"/>
     </row>
-    <row r="6" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -1761,7 +1767,9 @@
       <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="1"/>
@@ -1854,7 +1862,7 @@
       <c r="CU6" s="1"/>
       <c r="CV6" s="1"/>
     </row>
-    <row r="7" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1879,7 +1887,9 @@
       <c r="H7" s="2">
         <v>1</v>
       </c>
-      <c r="I7" s="2"/>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="1"/>
@@ -1972,7 +1982,7 @@
       <c r="CU7" s="1"/>
       <c r="CV7" s="1"/>
     </row>
-    <row r="8" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1997,7 +2007,9 @@
       <c r="H8" s="2">
         <v>1</v>
       </c>
-      <c r="I8" s="2"/>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="1"/>
@@ -2090,7 +2102,7 @@
       <c r="CU8" s="1"/>
       <c r="CV8" s="1"/>
     </row>
-    <row r="9" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -2115,7 +2127,9 @@
       <c r="H9" s="2">
         <v>1</v>
       </c>
-      <c r="I9" s="2"/>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="1"/>
@@ -2208,7 +2222,7 @@
       <c r="CU9" s="1"/>
       <c r="CV9" s="1"/>
     </row>
-    <row r="10" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
@@ -2233,7 +2247,9 @@
       <c r="H10" s="2">
         <v>0</v>
       </c>
-      <c r="I10" s="2"/>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="1"/>
@@ -2326,7 +2342,7 @@
       <c r="CU10" s="1"/>
       <c r="CV10" s="1"/>
     </row>
-    <row r="11" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -2351,7 +2367,9 @@
       <c r="H11" s="2">
         <v>1</v>
       </c>
-      <c r="I11" s="2"/>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="1"/>
@@ -2444,7 +2462,7 @@
       <c r="CU11" s="1"/>
       <c r="CV11" s="1"/>
     </row>
-    <row r="12" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -2469,7 +2487,9 @@
       <c r="H12" s="2">
         <v>1</v>
       </c>
-      <c r="I12" s="2"/>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="1"/>
@@ -2562,7 +2582,7 @@
       <c r="CU12" s="1"/>
       <c r="CV12" s="1"/>
     </row>
-    <row r="13" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>35</v>
       </c>
@@ -2587,7 +2607,9 @@
       <c r="H13" s="2">
         <v>1</v>
       </c>
-      <c r="I13" s="2"/>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="1"/>
@@ -2680,7 +2702,7 @@
       <c r="CU13" s="1"/>
       <c r="CV13" s="1"/>
     </row>
-    <row r="14" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>38</v>
       </c>
@@ -2705,7 +2727,9 @@
       <c r="H14" s="2">
         <v>1</v>
       </c>
-      <c r="I14" s="2"/>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="1"/>
@@ -2798,7 +2822,7 @@
       <c r="CU14" s="1"/>
       <c r="CV14" s="1"/>
     </row>
-    <row r="15" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
@@ -2823,7 +2847,9 @@
       <c r="H15" s="2">
         <v>0</v>
       </c>
-      <c r="I15" s="2"/>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="1"/>
@@ -2916,7 +2942,7 @@
       <c r="CU15" s="1"/>
       <c r="CV15" s="1"/>
     </row>
-    <row r="16" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>44</v>
       </c>
@@ -2941,7 +2967,9 @@
       <c r="H16" s="2">
         <v>1</v>
       </c>
-      <c r="I16" s="2"/>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="1"/>
@@ -3034,7 +3062,7 @@
       <c r="CU16" s="1"/>
       <c r="CV16" s="1"/>
     </row>
-    <row r="17" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
@@ -3059,7 +3087,9 @@
       <c r="H17" s="2">
         <v>1</v>
       </c>
-      <c r="I17" s="2"/>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="1"/>
@@ -3152,7 +3182,7 @@
       <c r="CU17" s="1"/>
       <c r="CV17" s="1"/>
     </row>
-    <row r="18" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>50</v>
       </c>
@@ -3177,7 +3207,9 @@
       <c r="H18" s="2">
         <v>1</v>
       </c>
-      <c r="I18" s="2"/>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="1"/>
@@ -3270,7 +3302,7 @@
       <c r="CU18" s="1"/>
       <c r="CV18" s="1"/>
     </row>
-    <row r="19" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>53</v>
       </c>
@@ -3295,7 +3327,9 @@
       <c r="H19" s="2">
         <v>1</v>
       </c>
-      <c r="I19" s="2"/>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="1"/>
@@ -3388,7 +3422,7 @@
       <c r="CU19" s="1"/>
       <c r="CV19" s="1"/>
     </row>
-    <row r="20" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>56</v>
       </c>
@@ -3413,7 +3447,9 @@
       <c r="H20" s="2">
         <v>0</v>
       </c>
-      <c r="I20" s="2"/>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="1"/>
@@ -3506,7 +3542,7 @@
       <c r="CU20" s="1"/>
       <c r="CV20" s="1"/>
     </row>
-    <row r="21" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>59</v>
       </c>
@@ -3531,7 +3567,9 @@
       <c r="H21" s="2">
         <v>1</v>
       </c>
-      <c r="I21" s="2"/>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="1"/>
@@ -3624,7 +3662,7 @@
       <c r="CU21" s="1"/>
       <c r="CV21" s="1"/>
     </row>
-    <row r="22" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>62</v>
       </c>
@@ -3649,7 +3687,9 @@
       <c r="H22" s="2">
         <v>1</v>
       </c>
-      <c r="I22" s="2"/>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="1"/>
@@ -3742,7 +3782,7 @@
       <c r="CU22" s="1"/>
       <c r="CV22" s="1"/>
     </row>
-    <row r="23" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>65</v>
       </c>
@@ -3767,7 +3807,9 @@
       <c r="H23" s="2">
         <v>1</v>
       </c>
-      <c r="I23" s="2"/>
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="1"/>
@@ -3860,7 +3902,7 @@
       <c r="CU23" s="1"/>
       <c r="CV23" s="1"/>
     </row>
-    <row r="24" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>68</v>
       </c>
@@ -3885,7 +3927,9 @@
       <c r="H24" s="2">
         <v>1</v>
       </c>
-      <c r="I24" s="2"/>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="1"/>
@@ -3978,7 +4022,7 @@
       <c r="CU24" s="1"/>
       <c r="CV24" s="1"/>
     </row>
-    <row r="25" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>71</v>
       </c>
@@ -4003,7 +4047,9 @@
       <c r="H25" s="2">
         <v>1</v>
       </c>
-      <c r="I25" s="2"/>
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="1"/>
@@ -4096,7 +4142,7 @@
       <c r="CU25" s="1"/>
       <c r="CV25" s="1"/>
     </row>
-    <row r="26" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>74</v>
       </c>
@@ -4121,7 +4167,9 @@
       <c r="H26" s="2">
         <v>1</v>
       </c>
-      <c r="I26" s="2"/>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="1"/>
@@ -4214,7 +4262,7 @@
       <c r="CU26" s="1"/>
       <c r="CV26" s="1"/>
     </row>
-    <row r="27" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>77</v>
       </c>
@@ -4239,7 +4287,9 @@
       <c r="H27" s="2">
         <v>0</v>
       </c>
-      <c r="I27" s="2"/>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="1"/>
@@ -4332,7 +4382,7 @@
       <c r="CU27" s="1"/>
       <c r="CV27" s="1"/>
     </row>
-    <row r="28" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>80</v>
       </c>
@@ -4357,7 +4407,9 @@
       <c r="H28" s="2">
         <v>0</v>
       </c>
-      <c r="I28" s="2"/>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="1"/>
@@ -4450,7 +4502,7 @@
       <c r="CU28" s="1"/>
       <c r="CV28" s="1"/>
     </row>
-    <row r="29" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>83</v>
       </c>
@@ -4475,7 +4527,9 @@
       <c r="H29" s="2">
         <v>1</v>
       </c>
-      <c r="I29" s="2"/>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
       <c r="L29" s="1"/>
@@ -4568,7 +4622,7 @@
       <c r="CU29" s="1"/>
       <c r="CV29" s="1"/>
     </row>
-    <row r="30" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>86</v>
       </c>
@@ -4593,7 +4647,9 @@
       <c r="H30" s="2">
         <v>1</v>
       </c>
-      <c r="I30" s="2"/>
+      <c r="I30" s="2">
+        <v>1</v>
+      </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="1"/>
@@ -4686,7 +4742,7 @@
       <c r="CU30" s="1"/>
       <c r="CV30" s="1"/>
     </row>
-    <row r="31" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>89</v>
       </c>
@@ -4711,7 +4767,9 @@
       <c r="H31" s="2">
         <v>1</v>
       </c>
-      <c r="I31" s="2"/>
+      <c r="I31" s="2">
+        <v>1</v>
+      </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="1"/>
@@ -4804,7 +4862,7 @@
       <c r="CU31" s="1"/>
       <c r="CV31" s="1"/>
     </row>
-    <row r="32" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>92</v>
       </c>
@@ -4829,7 +4887,9 @@
       <c r="H32" s="2">
         <v>1</v>
       </c>
-      <c r="I32" s="2"/>
+      <c r="I32" s="2">
+        <v>1</v>
+      </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="1"/>
@@ -4922,7 +4982,7 @@
       <c r="CU32" s="1"/>
       <c r="CV32" s="1"/>
     </row>
-    <row r="33" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>95</v>
       </c>
@@ -4947,7 +5007,9 @@
       <c r="H33" s="2">
         <v>1</v>
       </c>
-      <c r="I33" s="2"/>
+      <c r="I33" s="2">
+        <v>1</v>
+      </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="1"/>
@@ -5040,7 +5102,7 @@
       <c r="CU33" s="1"/>
       <c r="CV33" s="1"/>
     </row>
-    <row r="34" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>98</v>
       </c>
@@ -5065,7 +5127,9 @@
       <c r="H34" s="2">
         <v>1</v>
       </c>
-      <c r="I34" s="2"/>
+      <c r="I34" s="2">
+        <v>1</v>
+      </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
       <c r="L34" s="1"/>
@@ -5158,7 +5222,7 @@
       <c r="CU34" s="1"/>
       <c r="CV34" s="1"/>
     </row>
-    <row r="35" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>101</v>
       </c>
@@ -5183,7 +5247,9 @@
       <c r="H35" s="2">
         <v>1</v>
       </c>
-      <c r="I35" s="2"/>
+      <c r="I35" s="2">
+        <v>1</v>
+      </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
       <c r="L35" s="1"/>
@@ -5276,7 +5342,7 @@
       <c r="CU35" s="1"/>
       <c r="CV35" s="1"/>
     </row>
-    <row r="36" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>104</v>
       </c>
@@ -5301,7 +5367,9 @@
       <c r="H36" s="2">
         <v>1</v>
       </c>
-      <c r="I36" s="2"/>
+      <c r="I36" s="2">
+        <v>1</v>
+      </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="1"/>
@@ -5394,7 +5462,7 @@
       <c r="CU36" s="1"/>
       <c r="CV36" s="1"/>
     </row>
-    <row r="37" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>107</v>
       </c>
@@ -5419,7 +5487,9 @@
       <c r="H37" s="2">
         <v>1</v>
       </c>
-      <c r="I37" s="2"/>
+      <c r="I37" s="2">
+        <v>1</v>
+      </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="1"/>
@@ -5512,7 +5582,7 @@
       <c r="CU37" s="1"/>
       <c r="CV37" s="1"/>
     </row>
-    <row r="38" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>110</v>
       </c>
@@ -5537,7 +5607,9 @@
       <c r="H38" s="2">
         <v>1</v>
       </c>
-      <c r="I38" s="2"/>
+      <c r="I38" s="2">
+        <v>1</v>
+      </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="1"/>
@@ -5630,7 +5702,7 @@
       <c r="CU38" s="1"/>
       <c r="CV38" s="1"/>
     </row>
-    <row r="39" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>113</v>
       </c>
@@ -5655,7 +5727,9 @@
       <c r="H39" s="2">
         <v>0</v>
       </c>
-      <c r="I39" s="2"/>
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="1"/>
@@ -5748,7 +5822,7 @@
       <c r="CU39" s="1"/>
       <c r="CV39" s="1"/>
     </row>
-    <row r="40" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>116</v>
       </c>
@@ -5773,7 +5847,9 @@
       <c r="H40" s="2">
         <v>1</v>
       </c>
-      <c r="I40" s="2"/>
+      <c r="I40" s="2">
+        <v>1</v>
+      </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="1"/>
@@ -5866,7 +5942,7 @@
       <c r="CU40" s="1"/>
       <c r="CV40" s="1"/>
     </row>
-    <row r="41" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>119</v>
       </c>
@@ -5891,7 +5967,9 @@
       <c r="H41" s="2">
         <v>1</v>
       </c>
-      <c r="I41" s="2"/>
+      <c r="I41" s="2">
+        <v>1</v>
+      </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="1"/>
@@ -5984,7 +6062,7 @@
       <c r="CU41" s="1"/>
       <c r="CV41" s="1"/>
     </row>
-    <row r="42" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>122</v>
       </c>
@@ -6009,7 +6087,9 @@
       <c r="H42" s="2">
         <v>1</v>
       </c>
-      <c r="I42" s="2"/>
+      <c r="I42" s="2">
+        <v>1</v>
+      </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="1"/>
@@ -6102,7 +6182,7 @@
       <c r="CU42" s="1"/>
       <c r="CV42" s="1"/>
     </row>
-    <row r="43" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>125</v>
       </c>
@@ -6127,7 +6207,9 @@
       <c r="H43" s="2">
         <v>1</v>
       </c>
-      <c r="I43" s="2"/>
+      <c r="I43" s="2">
+        <v>1</v>
+      </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
       <c r="L43" s="1"/>
@@ -6220,7 +6302,7 @@
       <c r="CU43" s="1"/>
       <c r="CV43" s="1"/>
     </row>
-    <row r="44" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>128</v>
       </c>
@@ -6245,7 +6327,9 @@
       <c r="H44" s="2">
         <v>1</v>
       </c>
-      <c r="I44" s="2"/>
+      <c r="I44" s="2">
+        <v>1</v>
+      </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="1"/>
@@ -6338,7 +6422,7 @@
       <c r="CU44" s="1"/>
       <c r="CV44" s="1"/>
     </row>
-    <row r="45" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>131</v>
       </c>
@@ -6363,7 +6447,9 @@
       <c r="H45" s="2">
         <v>1</v>
       </c>
-      <c r="I45" s="2"/>
+      <c r="I45" s="2">
+        <v>1</v>
+      </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="1"/>
@@ -6456,7 +6542,7 @@
       <c r="CU45" s="1"/>
       <c r="CV45" s="1"/>
     </row>
-    <row r="46" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>134</v>
       </c>
@@ -6481,7 +6567,9 @@
       <c r="H46" s="2">
         <v>1</v>
       </c>
-      <c r="I46" s="2"/>
+      <c r="I46" s="2">
+        <v>1</v>
+      </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
       <c r="L46" s="1"/>
@@ -6574,7 +6662,7 @@
       <c r="CU46" s="1"/>
       <c r="CV46" s="1"/>
     </row>
-    <row r="47" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>137</v>
       </c>
@@ -6599,7 +6687,9 @@
       <c r="H47" s="2">
         <v>1</v>
       </c>
-      <c r="I47" s="2"/>
+      <c r="I47" s="2">
+        <v>1</v>
+      </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" s="1"/>
@@ -6692,7 +6782,7 @@
       <c r="CU47" s="1"/>
       <c r="CV47" s="1"/>
     </row>
-    <row r="48" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>140</v>
       </c>
@@ -6717,7 +6807,9 @@
       <c r="H48" s="2">
         <v>1</v>
       </c>
-      <c r="I48" s="2"/>
+      <c r="I48" s="2">
+        <v>1</v>
+      </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="1"/>
@@ -6810,7 +6902,7 @@
       <c r="CU48" s="1"/>
       <c r="CV48" s="1"/>
     </row>
-    <row r="49" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>143</v>
       </c>
@@ -6835,7 +6927,9 @@
       <c r="H49" s="2">
         <v>1</v>
       </c>
-      <c r="I49" s="2"/>
+      <c r="I49" s="2">
+        <v>1</v>
+      </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" s="1"/>
@@ -6928,7 +7022,7 @@
       <c r="CU49" s="1"/>
       <c r="CV49" s="1"/>
     </row>
-    <row r="50" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>145</v>
       </c>
@@ -6953,7 +7047,9 @@
       <c r="H50" s="2">
         <v>1</v>
       </c>
-      <c r="I50" s="2"/>
+      <c r="I50" s="2">
+        <v>1</v>
+      </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="1"/>
@@ -7046,7 +7142,7 @@
       <c r="CU50" s="1"/>
       <c r="CV50" s="1"/>
     </row>
-    <row r="51" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>148</v>
       </c>
@@ -7071,7 +7167,9 @@
       <c r="H51" s="2">
         <v>1</v>
       </c>
-      <c r="I51" s="2"/>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="1"/>
@@ -7164,7 +7262,7 @@
       <c r="CU51" s="1"/>
       <c r="CV51" s="1"/>
     </row>
-    <row r="52" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>151</v>
       </c>
@@ -7189,7 +7287,9 @@
       <c r="H52" s="2">
         <v>0</v>
       </c>
-      <c r="I52" s="2"/>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="1"/>
@@ -7282,7 +7382,7 @@
       <c r="CU52" s="1"/>
       <c r="CV52" s="1"/>
     </row>
-    <row r="53" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>154</v>
       </c>
@@ -7307,7 +7407,9 @@
       <c r="H53" s="2">
         <v>1</v>
       </c>
-      <c r="I53" s="2"/>
+      <c r="I53" s="2">
+        <v>1</v>
+      </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="1"/>
@@ -7400,7 +7502,7 @@
       <c r="CU53" s="1"/>
       <c r="CV53" s="1"/>
     </row>
-    <row r="54" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>157</v>
       </c>
@@ -7425,7 +7527,9 @@
       <c r="H54" s="2">
         <v>1</v>
       </c>
-      <c r="I54" s="2"/>
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="1"/>
@@ -7518,7 +7622,7 @@
       <c r="CU54" s="1"/>
       <c r="CV54" s="1"/>
     </row>
-    <row r="55" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>160</v>
       </c>
@@ -7543,7 +7647,9 @@
       <c r="H55" s="2">
         <v>1</v>
       </c>
-      <c r="I55" s="2"/>
+      <c r="I55" s="2">
+        <v>1</v>
+      </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="1"/>
@@ -7636,7 +7742,7 @@
       <c r="CU55" s="1"/>
       <c r="CV55" s="1"/>
     </row>
-    <row r="56" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>163</v>
       </c>
@@ -7661,7 +7767,9 @@
       <c r="H56" s="2">
         <v>1</v>
       </c>
-      <c r="I56" s="2"/>
+      <c r="I56" s="2">
+        <v>1</v>
+      </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="1"/>
@@ -7754,7 +7862,7 @@
       <c r="CU56" s="1"/>
       <c r="CV56" s="1"/>
     </row>
-    <row r="57" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>166</v>
       </c>
@@ -7779,7 +7887,9 @@
       <c r="H57" s="2">
         <v>1</v>
       </c>
-      <c r="I57" s="2"/>
+      <c r="I57" s="2">
+        <v>1</v>
+      </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
       <c r="L57" s="1"/>
@@ -7872,7 +7982,7 @@
       <c r="CU57" s="1"/>
       <c r="CV57" s="1"/>
     </row>
-    <row r="58" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>169</v>
       </c>
@@ -7897,7 +8007,9 @@
       <c r="H58" s="2">
         <v>1</v>
       </c>
-      <c r="I58" s="2"/>
+      <c r="I58" s="2">
+        <v>1</v>
+      </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
       <c r="L58" s="1"/>
@@ -7990,7 +8102,7 @@
       <c r="CU58" s="1"/>
       <c r="CV58" s="1"/>
     </row>
-    <row r="59" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>172</v>
       </c>
@@ -8015,7 +8127,9 @@
       <c r="H59" s="2">
         <v>1</v>
       </c>
-      <c r="I59" s="2"/>
+      <c r="I59" s="2">
+        <v>1</v>
+      </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="1"/>
@@ -8108,7 +8222,7 @@
       <c r="CU59" s="1"/>
       <c r="CV59" s="1"/>
     </row>
-    <row r="60" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>175</v>
       </c>
@@ -8133,7 +8247,9 @@
       <c r="H60" s="2">
         <v>1</v>
       </c>
-      <c r="I60" s="2"/>
+      <c r="I60" s="2">
+        <v>1</v>
+      </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="1"/>
@@ -8226,7 +8342,7 @@
       <c r="CU60" s="1"/>
       <c r="CV60" s="1"/>
     </row>
-    <row r="61" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>178</v>
       </c>
@@ -8251,7 +8367,9 @@
       <c r="H61" s="2">
         <v>1</v>
       </c>
-      <c r="I61" s="2"/>
+      <c r="I61" s="2">
+        <v>1</v>
+      </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="1"/>
@@ -8344,7 +8462,7 @@
       <c r="CU61" s="1"/>
       <c r="CV61" s="1"/>
     </row>
-    <row r="62" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>181</v>
       </c>
@@ -8369,7 +8487,9 @@
       <c r="H62" s="2">
         <v>1</v>
       </c>
-      <c r="I62" s="2"/>
+      <c r="I62" s="2">
+        <v>1</v>
+      </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
       <c r="L62" s="1"/>
@@ -8462,7 +8582,7 @@
       <c r="CU62" s="1"/>
       <c r="CV62" s="1"/>
     </row>
-    <row r="63" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>184</v>
       </c>
@@ -8487,7 +8607,9 @@
       <c r="H63" s="2">
         <v>1</v>
       </c>
-      <c r="I63" s="2"/>
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
       <c r="L63" s="1"/>
@@ -8580,7 +8702,7 @@
       <c r="CU63" s="1"/>
       <c r="CV63" s="1"/>
     </row>
-    <row r="64" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>187</v>
       </c>
@@ -8605,7 +8727,9 @@
       <c r="H64" s="2">
         <v>1</v>
       </c>
-      <c r="I64" s="2"/>
+      <c r="I64" s="2">
+        <v>1</v>
+      </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
       <c r="L64" s="1"/>
@@ -8698,7 +8822,7 @@
       <c r="CU64" s="1"/>
       <c r="CV64" s="1"/>
     </row>
-    <row r="65" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>190</v>
       </c>
@@ -8723,7 +8847,9 @@
       <c r="H65" s="2">
         <v>1</v>
       </c>
-      <c r="I65" s="2"/>
+      <c r="I65" s="2">
+        <v>1</v>
+      </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
       <c r="L65" s="1"/>
@@ -8816,7 +8942,7 @@
       <c r="CU65" s="1"/>
       <c r="CV65" s="1"/>
     </row>
-    <row r="66" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>193</v>
       </c>
@@ -8841,7 +8967,9 @@
       <c r="H66" s="2">
         <v>1</v>
       </c>
-      <c r="I66" s="2"/>
+      <c r="I66" s="2">
+        <v>1</v>
+      </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
       <c r="L66" s="1"/>
@@ -8934,7 +9062,7 @@
       <c r="CU66" s="1"/>
       <c r="CV66" s="1"/>
     </row>
-    <row r="67" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>196</v>
       </c>
@@ -8959,7 +9087,9 @@
       <c r="H67" s="2">
         <v>1</v>
       </c>
-      <c r="I67" s="2"/>
+      <c r="I67" s="2">
+        <v>1</v>
+      </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
       <c r="L67" s="1"/>
@@ -9052,7 +9182,7 @@
       <c r="CU67" s="1"/>
       <c r="CV67" s="1"/>
     </row>
-    <row r="68" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>199</v>
       </c>
@@ -9077,7 +9207,9 @@
       <c r="H68" s="2">
         <v>1</v>
       </c>
-      <c r="I68" s="2"/>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
       <c r="L68" s="1"/>
@@ -9170,7 +9302,7 @@
       <c r="CU68" s="1"/>
       <c r="CV68" s="1"/>
     </row>
-    <row r="69" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>202</v>
       </c>
@@ -9195,7 +9327,9 @@
       <c r="H69" s="2">
         <v>1</v>
       </c>
-      <c r="I69" s="2"/>
+      <c r="I69" s="2">
+        <v>1</v>
+      </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
       <c r="L69" s="1"/>
@@ -9288,7 +9422,7 @@
       <c r="CU69" s="1"/>
       <c r="CV69" s="1"/>
     </row>
-    <row r="70" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>205</v>
       </c>
@@ -9313,7 +9447,9 @@
       <c r="H70" s="2">
         <v>1</v>
       </c>
-      <c r="I70" s="2"/>
+      <c r="I70" s="2">
+        <v>1</v>
+      </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
       <c r="L70" s="1"/>
@@ -9406,7 +9542,7 @@
       <c r="CU70" s="1"/>
       <c r="CV70" s="1"/>
     </row>
-    <row r="71" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>208</v>
       </c>
@@ -9431,7 +9567,9 @@
       <c r="H71" s="2">
         <v>1</v>
       </c>
-      <c r="I71" s="2"/>
+      <c r="I71" s="2">
+        <v>1</v>
+      </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
       <c r="L71" s="1"/>
@@ -9524,7 +9662,7 @@
       <c r="CU71" s="1"/>
       <c r="CV71" s="1"/>
     </row>
-    <row r="72" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>211</v>
       </c>
@@ -9549,7 +9687,9 @@
       <c r="H72" s="2">
         <v>1</v>
       </c>
-      <c r="I72" s="2"/>
+      <c r="I72" s="2">
+        <v>1</v>
+      </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
       <c r="L72" s="1"/>
@@ -9642,7 +9782,7 @@
       <c r="CU72" s="1"/>
       <c r="CV72" s="1"/>
     </row>
-    <row r="73" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -9744,7 +9884,7 @@
       <c r="CU73" s="1"/>
       <c r="CV73" s="1"/>
     </row>
-    <row r="74" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -9846,7 +9986,7 @@
       <c r="CU74" s="1"/>
       <c r="CV74" s="1"/>
     </row>
-    <row r="75" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -9948,7 +10088,7 @@
       <c r="CU75" s="1"/>
       <c r="CV75" s="1"/>
     </row>
-    <row r="76" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -10050,7 +10190,7 @@
       <c r="CU76" s="1"/>
       <c r="CV76" s="1"/>
     </row>
-    <row r="77" spans="1:100" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
